--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>774.97</v>
+        <v>770.98</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4312.16</v>
+        <v>4290.01</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24952.29</v>
+        <v>24690.99</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>981.87</v>
+        <v>971.59</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2985.96</v>
+        <v>2969.64</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5879.93</v>
+        <v>5814.42</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2096.81</v>
+        <v>2119.61</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3207.43</v>
+        <v>3217.97</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3261.41</v>
+        <v>3272.14</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>859.14</v>
+        <v>861.97</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6234.8</v>
+        <v>6255.31</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5374.22</v>
+        <v>5411.45</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>821.1900000000001</v>
+        <v>825.02</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>953.12</v>
+        <v>959.99</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>973.64</v>
+        <v>980.51</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10740.45</v>
+        <v>10604.02</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2153.21</v>
+        <v>2125.86</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4126.47</v>
+        <v>4074.06</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3164.65</v>
+        <v>3157.8</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1617.27</v>
+        <v>1613.77</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1700.9</v>
+        <v>1681.22</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1972.5</v>
+        <v>1970.92</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1472.44</v>
+        <v>1476.35</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6548.98</v>
+        <v>6566.35</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2639.36</v>
+        <v>2657.52</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4817.86</v>
+        <v>4851.03</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1375.3</v>
+        <v>1387.05</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>900.78</v>
+        <v>908.48</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1309.25</v>
+        <v>1320.44</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1889.92</v>
+        <v>1913.15</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4760.32</v>
+        <v>4821.49</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>10458</v>
+        <v>10472.52</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>27385.14</v>
+        <v>27366.43</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>23204.72</v>
+        <v>23125.08</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1647.81</v>
+        <v>1639.1</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12513.68</v>
+        <v>12435.26</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2721.59</v>
+        <v>2790.39</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2243.25</v>
+        <v>2311.27</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>815.9</v>
+        <v>840.64</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>846.49</v>
+        <v>871.65</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4801.24</v>
+        <v>4943.95</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>8059.45</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1128.21</v>
+        <v>1124.2</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1046.32</v>
+        <v>1042.59</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1749.11</v>
+        <v>1754.17</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8197.4</v>
+        <v>8239.74</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1574.19</v>
+        <v>1582.32</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>12501.61</v>
+        <v>12448.9</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4118.87</v>
+        <v>4147.55</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1984.78</v>
+        <v>1997.85</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1296.1</v>
+        <v>1304.63</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>13712.57</v>
+        <v>13834.7</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>12423.69</v>
+        <v>12402.4</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>11053.35</v>
+        <v>11034.41</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2397.29</v>
+        <v>2380.12</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2326.1</v>
+        <v>2322.68</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>103617.74</v>
+        <v>103053.47</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3986.83</v>
+        <v>3963.33</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>929.08</v>
+        <v>923.61</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6216.98</v>
+        <v>6180.35</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8031.04</v>
+        <v>8000.05</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7759.02</v>
+        <v>7729.08</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>12277.63</v>
+        <v>12289.46</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4439.33</v>
+        <v>4443.61</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>869.91</v>
+        <v>870.75</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3788.04</v>
+        <v>3791.69</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>901.21</v>
+        <v>941.01</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>9029.33</v>
+        <v>9051.549999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1137.69</v>
+        <v>1140.49</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>22809.22</v>
+        <v>22515.58</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9015.389999999999</v>
+        <v>8899.32</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>856.9</v>
+        <v>857.64</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1821.54</v>
+        <v>1811.08</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4492.47</v>
+        <v>4463.69</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>5839.57</v>
+        <v>5814.41</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1730.9</v>
+        <v>1690.63</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1127.9</v>
+        <v>1105.65</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1602.33</v>
+        <v>1559.43</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2381.03</v>
+        <v>2317.28</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4785.52</v>
+        <v>4657.38</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5437.19</v>
+        <v>5483.33</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1771.31</v>
+        <v>1793.11</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>18750.87</v>
+        <v>18995.56</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1056.32</v>
+        <v>1076.29</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5873.18</v>
+        <v>5926.09</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5872.45</v>
+        <v>5890.92</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3157.15</v>
+        <v>3170.23</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1848.98</v>
+        <v>1852.81</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4465.61</v>
+        <v>4404.9</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>6726.16</v>
+        <v>6634.71</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1331.67</v>
+        <v>1313.56</v>
       </c>
     </row>
     <row r="93">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5760.18</v>
+        <v>5711.05</v>
       </c>
     </row>
     <row r="94">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8035.21</v>
+        <v>7966.67</v>
       </c>
     </row>
     <row r="95">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4076.87</v>
+        <v>4098.82</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>14304.55</v>
+        <v>14440.45</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1113.91</v>
+        <v>1124.49</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>16605.78</v>
+        <v>16425.14</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1452.14</v>
+        <v>1448.55</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1143.13</v>
+        <v>1146.92</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>11870.07</v>
+        <v>11909.44</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1596.21</v>
+        <v>1601.29</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>15244.03</v>
+        <v>15462.16</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>4675.44</v>
+        <v>4609.09</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>11176.76</v>
+        <v>11018.14</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4982.03</v>
+        <v>4913.58</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1475.05</v>
+        <v>1454.78</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2907.41</v>
+        <v>2867.46</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6310.52</v>
+        <v>6271.4</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>38425.79</v>
+        <v>39156.32</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4904.32</v>
+        <v>4997.56</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>8002.44</v>
+        <v>8154.58</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1875.43</v>
+        <v>1917.72</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2729.07</v>
+        <v>2747.91</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1990.11</v>
+        <v>2003.85</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>791.86</v>
+        <v>797.33</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2475.13</v>
+        <v>2492.22</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2605.56</v>
+        <v>2613.61</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3545.72</v>
+        <v>3536.34</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3351.79</v>
+        <v>3342.92</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1924.52</v>
+        <v>1898.89</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>12967.39</v>
+        <v>12794.66</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2051.09</v>
+        <v>2023.77</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2823.62</v>
+        <v>2852.02</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>826.99</v>
+        <v>835.3</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>6441.67</v>
+        <v>6506.18</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>9767.940000000001</v>
+        <v>9865.75</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5364.12</v>
+        <v>5417.83</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>12364.38</v>
+        <v>12444.99</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>11307.92</v>
+        <v>11381.64</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>19891.1</v>
+        <v>20020.78</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3620.13</v>
+        <v>3612.87</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2458.05</v>
+        <v>2429.45</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2228.86</v>
+        <v>2202.93</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2562.35</v>
+        <v>2532.54</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1186.23</v>
+        <v>1180.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3265-2057-CM25</t>
+          <t>3593-167-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>770.98</v>
+        <v>6063.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3512-5668-CM25</t>
+          <t>3512-4895-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4290.01</v>
+        <v>3672.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2446-1830-CM25</t>
+          <t>1232565-156-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24690.99</v>
+        <v>1460.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1159-240-CM25</t>
+          <t>3512-5551-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>971.59</v>
+        <v>3035.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3512-5693-CM25</t>
+          <t>3509-622-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2969.64</v>
+        <v>1149.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3512-5697-CM25</t>
+          <t>3512-5668-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5814.42</v>
+        <v>4290.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3512-5728-CM25</t>
+          <t>3265-2057-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2119.61</v>
+        <v>770.98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1698-323-CM25</t>
+          <t>2446-1830-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3217.97</v>
+        <v>24690.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>646-137-CM25</t>
+          <t>1159-240-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3272.14</v>
+        <v>971.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3512-5742-CM25</t>
+          <t>3512-5693-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>861.97</v>
+        <v>2969.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3512-5748-CM25</t>
+          <t>3512-5697-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6255.31</v>
+        <v>5814.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1159-258-CM25</t>
+          <t>3512-5728-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA PROINMIN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.949.422-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5411.45</v>
+        <v>2119.61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3512-5785-CM25</t>
+          <t>3512-5748-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>825.02</v>
+        <v>6255.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1058900-101-CM25</t>
+          <t>646-137-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>959.99</v>
+        <v>3272.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1574-340-CM25</t>
+          <t>1698-323-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>980.51</v>
+        <v>3217.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3512-5858-CM25</t>
+          <t>3512-5742-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10604.02</v>
+        <v>861.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3712-1080-CM25</t>
+          <t>1159-258-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA PROINMIN SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.949.422-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2125.86</v>
+        <v>5411.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3712-1068-CM25</t>
+          <t>3512-5785-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4074.06</v>
+        <v>825.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3512-5880-CM25</t>
+          <t>1058900-101-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3157.8</v>
+        <v>959.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3511-795-CM25</t>
+          <t>1574-340-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1613.77</v>
+        <v>980.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4619-42-CM25</t>
+          <t>3712-1068-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1681.22</v>
+        <v>4074.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3512-5894-CM25</t>
+          <t>3712-1080-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1970.92</v>
+        <v>2125.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3512-5903-CM25</t>
+          <t>3512-5858-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1476.35</v>
+        <v>10604.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3512-5905-CM25</t>
+          <t>3512-5880-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6566.35</v>
+        <v>3157.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2555-266-CM25</t>
+          <t>3511-795-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2657.52</v>
+        <v>1613.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2555-1792-CM25</t>
+          <t>4619-42-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4851.03</v>
+        <v>1681.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2711-615-CM25</t>
+          <t>3512-5894-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1387.05</v>
+        <v>1970.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3511-810-CM25</t>
+          <t>3512-5903-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>908.48</v>
+        <v>1476.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>707418-236-CM25</t>
+          <t>3512-5905-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1320.44</v>
+        <v>6566.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3512-5932-CM25</t>
+          <t>2555-266-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,22 +2298,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1913.15</v>
+        <v>2657.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1461054-720-CM25</t>
+          <t>2555-1792-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4821.49</v>
+        <v>4851.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1159-4-CM26</t>
+          <t>2711-615-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>10472.52</v>
+        <v>1387.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3714-2-CM26</t>
+          <t>3511-810-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>27366.43</v>
+        <v>908.48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1159-7-CM26</t>
+          <t>707418-236-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>23125.08</v>
+        <v>1320.44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3512-44-CM26</t>
+          <t>3512-5932-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1639.1</v>
+        <v>1913.15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3512-45-CM26</t>
+          <t>1461054-720-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12435.26</v>
+        <v>4821.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3511-9-CM26</t>
+          <t>1159-4-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2790.39</v>
+        <v>10472.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3511-10-CM26</t>
+          <t>3714-2-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,22 +2786,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2311.27</v>
+        <v>27366.43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3512-69-CM26</t>
+          <t>1159-7-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>840.64</v>
+        <v>23125.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3512-80-CM26</t>
+          <t>3512-44-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>871.65</v>
+        <v>1639.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3512-88-CM26</t>
+          <t>3512-45-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4943.95</v>
+        <v>12435.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3512-91-CM26</t>
+          <t>3511-9-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>8299</v>
+        <v>2790.39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3511-17-CM26</t>
+          <t>3511-10-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1124.2</v>
+        <v>2311.27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3511-18-CM26</t>
+          <t>3512-69-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1042.59</v>
+        <v>840.64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3511-24-CM26</t>
+          <t>3512-80-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1754.17</v>
+        <v>871.65</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3512-112-CM26</t>
+          <t>3512-88-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8239.74</v>
+        <v>4943.95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3511-25-CM26</t>
+          <t>3512-91-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1582.32</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>627786-29-CM26</t>
+          <t>3511-17-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,22 +3396,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LORENZINI PAGLIETTINI Y CIA LTDA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>80.565.500-3</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>12448.9</v>
+        <v>1124.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3512-140-CM26</t>
+          <t>3511-18-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4147.55</v>
+        <v>1042.59</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3512-159-CM26</t>
+          <t>3511-24-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1997.85</v>
+        <v>1754.17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3512-158-CM26</t>
+          <t>3512-112-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1304.63</v>
+        <v>8239.74</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1159-30-CM26</t>
+          <t>3511-25-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>13834.7</v>
+        <v>1582.32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3714-6-CM26</t>
+          <t>627786-29-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>Carabineros de Chile - Prefectura Coquimbo</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>LORENZINI PAGLIETTINI Y CIA LTDA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>80.565.500-3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>12402.4</v>
+        <v>12448.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3714-21-CM26</t>
+          <t>3512-140-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>11034.41</v>
+        <v>4147.55</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3511-40-CM26</t>
+          <t>3512-158-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2380.12</v>
+        <v>1304.63</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3512-192-CM26</t>
+          <t>3512-159-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2322.68</v>
+        <v>1997.85</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4295-1-CM26</t>
+          <t>1159-30-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,32 +3970,28 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MOTORSHOP</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.193.188-1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>103053.47</v>
+        <v>13834.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3512-199-CM26</t>
+          <t>3714-6-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4010,22 +4006,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4050,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3963.33</v>
+        <v>12402.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3511-42-CM26</t>
+          <t>3714-21-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4071,22 +4067,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>923.61</v>
+        <v>11034.41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3512-200-CM26</t>
+          <t>3511-40-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4132,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4157,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4172,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6180.35</v>
+        <v>2380.12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2446-176-CM26</t>
+          <t>3512-192-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4193,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4203,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8000.05</v>
+        <v>2322.68</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2446-177-CM26</t>
+          <t>4295-1-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4254,22 +4250,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,28 +4275,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>MOTORSHOP</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>76.193.188-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7729.08</v>
+        <v>103053.47</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>627786-33-CM26</t>
+          <t>3511-42-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4315,22 +4315,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>12289.46</v>
+        <v>923.61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1159-36-CM26</t>
+          <t>3512-199-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4443.61</v>
+        <v>3963.33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3512-223-CM26</t>
+          <t>3512-200-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>870.75</v>
+        <v>6180.35</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3512-227-CM26</t>
+          <t>2446-176-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>84.634.200-1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3791.69</v>
+        <v>8000.05</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1159-38-CM26</t>
+          <t>2446-177-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4554,27 +4554,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>941.01</v>
+        <v>7729.08</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1002588-43-CM26</t>
+          <t>3512-227-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4615,27 +4615,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>9051.549999999999</v>
+        <v>3791.69</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1002588-42-CM26</t>
+          <t>3512-223-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4676,27 +4676,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1140.49</v>
+        <v>870.75</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1159-49-CM26</t>
+          <t>1159-36-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>22515.58</v>
+        <v>4443.61</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3682-223-CM26</t>
+          <t>627786-33-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>Carabineros de Chile - Prefectura Coquimbo</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>8899.32</v>
+        <v>12289.46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1430707-1008-CM26</t>
+          <t>1159-38-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4864,22 +4864,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>857.64</v>
+        <v>941.01</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3512-330-CM26</t>
+          <t>1002588-42-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4925,22 +4925,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1811.08</v>
+        <v>1140.49</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3511-78-CM26</t>
+          <t>1002588-43-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4986,22 +4986,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5026,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4463.69</v>
+        <v>9051.549999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3512-347-CM26</t>
+          <t>1159-49-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>5814.41</v>
+        <v>22515.58</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3512-365-CM26</t>
+          <t>3682-223-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5108,22 +5108,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1690.63</v>
+        <v>8899.32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1173458-2-CM26</t>
+          <t>1430707-1008-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.980.390-6</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1105.65</v>
+        <v>857.64</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3712-248-CM26</t>
+          <t>3512-330-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5225,27 +5225,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1559.43</v>
+        <v>1811.08</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2446-366-CM26</t>
+          <t>3511-78-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5286,27 +5286,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2317.28</v>
+        <v>4463.69</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2708-194-CM26</t>
+          <t>3512-347-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4657.38</v>
+        <v>5814.41</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3000-454-CM26</t>
+          <t>3512-365-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5483.33</v>
+        <v>1690.63</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2555-57-CM26</t>
+          <t>1173458-2-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.390-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Centro de Educación y Trabajo CDP Ovalle</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1793.11</v>
+        <v>1105.65</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1079505-152-CM26</t>
+          <t>3712-248-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>18995.56</v>
+        <v>1559.43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3511-125-CM26</t>
+          <t>2446-366-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5596,22 +5596,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,13 +5636,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1076.29</v>
+        <v>2317.28</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3714-108-CM26</t>
+          <t>2708-194-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5657,22 +5657,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5926.09</v>
+        <v>4657.38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3512-437-CM26</t>
+          <t>3000-454-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5890.92</v>
+        <v>5483.33</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3712-297-CM26</t>
+          <t>2555-57-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3170.23</v>
+        <v>1793.11</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4036-226-CM26</t>
+          <t>1079505-152-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5840,22 +5840,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1852.81</v>
+        <v>18995.56</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3512-450-CM26</t>
+          <t>3511-125-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4404.9</v>
+        <v>1076.29</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3512-460-CM26</t>
+          <t>3714-108-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5957,27 +5957,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>6634.71</v>
+        <v>5926.09</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2555-66-CM26</t>
+          <t>3512-437-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6018,27 +6018,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1313.56</v>
+        <v>5890.92</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3712-332-CM26</t>
+          <t>3712-297-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5711.05</v>
+        <v>3170.23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3512-447-CM26</t>
+          <t>4036-226-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>7966.67</v>
+        <v>1852.81</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>646-50-CM26</t>
+          <t>2555-66-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4098.82</v>
+        <v>1313.56</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1057439-3336-CM26</t>
+          <t>3512-460-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6267,22 +6267,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>14440.45</v>
+        <v>6634.71</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1962-268-CM26</t>
+          <t>3512-450-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6328,22 +6328,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6368,13 +6368,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1124.49</v>
+        <v>4404.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1159-106-CM26</t>
+          <t>3712-332-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6389,22 +6389,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>16425.14</v>
+        <v>5711.05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>894358-22-CM26</t>
+          <t>3512-447-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6450,22 +6450,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1448.55</v>
+        <v>7966.67</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>627786-92-CM26</t>
+          <t>646-50-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1146.92</v>
+        <v>4098.82</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>627786-96-CM26</t>
+          <t>1057439-3336-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>11909.44</v>
+        <v>14440.45</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1159-113-CM26</t>
+          <t>1962-268-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6633,22 +6633,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1601.29</v>
+        <v>1124.49</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1159-114-CM26</t>
+          <t>1159-106-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>15462.16</v>
+        <v>16425.14</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1574-75-CM26</t>
+          <t>894358-22-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Servicio Electoral</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>4609.09</v>
+        <v>1448.55</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1159-138-CM26</t>
+          <t>627786-96-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6811,27 +6811,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Carabineros de Chile - Prefectura Coquimbo</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>11018.14</v>
+        <v>11909.44</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3712-402-CM26</t>
+          <t>627786-92-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>Carabineros de Chile - Prefectura Coquimbo</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>MOTORSHOP</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.193.188-1</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4913.58</v>
+        <v>1146.92</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3512-547-CM26</t>
+          <t>1159-113-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1454.78</v>
+        <v>1601.29</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3512-559-CM26</t>
+          <t>1159-114-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2867.46</v>
+        <v>15462.16</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3512-549-CM26</t>
+          <t>1574-75-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7060,22 +7060,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6271.4</v>
+        <v>4609.09</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2446-644-CM26</t>
+          <t>1159-138-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7121,22 +7121,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>39156.32</v>
+        <v>11018.14</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3512-560-CM26</t>
+          <t>3712-402-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7182,22 +7182,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>MOTORSHOP</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.193.188-1</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4997.56</v>
+        <v>4913.58</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3512-574-CM26</t>
+          <t>3512-547-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>8154.58</v>
+        <v>1454.78</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1698-157-CM26</t>
+          <t>3512-559-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1917.72</v>
+        <v>2867.46</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3712-422-CM26</t>
+          <t>3512-549-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7365,22 +7365,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2747.91</v>
+        <v>6271.4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1574-84-CM26</t>
+          <t>2446-644-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2003.85</v>
+        <v>39156.32</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1574-85-CM26</t>
+          <t>3512-560-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7487,22 +7487,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>797.33</v>
+        <v>4997.56</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1232565-171-CM26</t>
+          <t>3512-574-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7548,22 +7548,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2492.22</v>
+        <v>8154.58</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1232565-175-CM26</t>
+          <t>1698-157-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2613.61</v>
+        <v>1917.72</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3512-590-CM26</t>
+          <t>1232565-171-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7670,22 +7670,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3536.34</v>
+        <v>2492.22</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3512-562-CM26</t>
+          <t>1574-85-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7731,22 +7731,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3342.92</v>
+        <v>797.33</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3712-453-CM26</t>
+          <t>3712-422-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1898.89</v>
+        <v>2747.91</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3000-716-CM26</t>
+          <t>1574-84-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7853,22 +7853,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>12794.66</v>
+        <v>2003.85</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1159-170-CM26</t>
+          <t>1232565-175-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7954,13 +7954,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2023.77</v>
+        <v>2613.61</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3712-451-CM26</t>
+          <t>3512-562-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7970,27 +7970,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES TASICA SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.268.885-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2852.02</v>
+        <v>3342.92</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>707418-92-CM26</t>
+          <t>3512-590-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>835.3</v>
+        <v>3536.34</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2446-762-CM26</t>
+          <t>3712-453-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8092,27 +8092,27 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>6506.18</v>
+        <v>1898.89</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3687-181-CM26</t>
+          <t>3000-716-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>9865.75</v>
+        <v>12794.66</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2446-761-CM26</t>
+          <t>1159-170-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8214,27 +8214,27 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8259,13 +8259,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5417.83</v>
+        <v>2023.77</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3712-478-CM26</t>
+          <t>3712-451-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>SOCIEDAD DE INVERSIONES TASICA SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.268.885-7</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8320,13 +8320,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>12444.99</v>
+        <v>2852.02</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3712-492-CM26</t>
+          <t>707418-92-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>11381.64</v>
+        <v>835.3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2446-802-CM26</t>
+          <t>3687-181-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8402,22 +8402,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>20020.78</v>
+        <v>9865.75</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1461054-282-CM26</t>
+          <t>2446-761-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8463,22 +8463,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3612.87</v>
+        <v>5417.83</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3512-694-CM26</t>
+          <t>2446-762-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2429.45</v>
+        <v>6506.18</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2446-852-CM26</t>
+          <t>3712-492-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2202.93</v>
+        <v>11381.64</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1430715-156-CM26</t>
+          <t>3712-478-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2532.54</v>
+        <v>12444.99</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2448-779-CM26</t>
+          <t>2446-802-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8747,6 +8747,311 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
+        <v>20020.78</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1461054-282-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>3612.87</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>3512-694-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>2429.45</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2446-852-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>2202.93</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1430715-156-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>61.606.403-7</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>2532.54</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2448-779-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
         <v>1180.4</v>
       </c>
     </row>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M262"/>
+  <dimension ref="A1:M288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1612,7 +1612,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1346282-84-CM25</t>
+          <t>3512-2795-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,17 +1632,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.967.556-6</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1812.83</v>
+        <v>4901.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3512-2795-CM25</t>
+          <t>1346282-84-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4901.83</v>
+        <v>1812.83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2446-265-CM25</t>
+          <t>2446-266-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7285.93</v>
+        <v>6648.29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2446-266-CM25</t>
+          <t>2446-265-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6648.29</v>
+        <v>7285.93</v>
       </c>
     </row>
     <row r="24">
@@ -2039,7 +2039,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3509-147-CM25</t>
+          <t>1962-140-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>10525.94</v>
+        <v>1260.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1962-140-CM25</t>
+          <t>3509-147-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1260.36</v>
+        <v>10525.94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3714-72-CM25</t>
+          <t>2446-264-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>QUALITY RUBBER S.A.</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>84.634.200-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7323.79</v>
+        <v>39871.31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2446-264-CM25</t>
+          <t>3714-72-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
+          <t>76.097.502-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>39871.31</v>
+        <v>7323.79</v>
       </c>
     </row>
     <row r="31">
@@ -3564,7 +3564,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1159-74-CM25</t>
+          <t>3597-354-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3584,17 +3584,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>21165.34</v>
+        <v>1395.03</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3597-354-CM25</t>
+          <t>1159-74-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1395.03</v>
+        <v>21165.34</v>
       </c>
     </row>
     <row r="54">
@@ -5577,7 +5577,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>539119-4678-CM25</t>
+          <t>539119-4673-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2916.95</v>
+        <v>1057.61</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>539119-4681-CM25</t>
+          <t>539119-4678-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3597.72</v>
+        <v>2916.95</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2708-702-CM25</t>
+          <t>539119-4681-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2039.87</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>539119-4673-CM25</t>
+          <t>2708-702-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5780,17 +5780,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1057.61</v>
+        <v>2039.87</v>
       </c>
     </row>
     <row r="89">
@@ -6065,7 +6065,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3512-5482-CM25</t>
+          <t>3712-852-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1308.95</v>
+        <v>6446.52</v>
       </c>
     </row>
     <row r="94">
@@ -6187,7 +6187,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3712-852-CM25</t>
+          <t>3512-5482-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>6446.52</v>
+        <v>1308.95</v>
       </c>
     </row>
     <row r="96">
@@ -6309,7 +6309,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1159-219-CM25</t>
+          <t>707418-153-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6329,17 +6329,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>16038.33</v>
+        <v>3146.58</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3512-5551-CM25</t>
+          <t>1159-219-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3035.48</v>
+        <v>16038.33</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>707418-153-CM25</t>
+          <t>3512-5551-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6451,17 +6451,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3146.58</v>
+        <v>3035.48</v>
       </c>
     </row>
     <row r="100">
@@ -7655,7 +7655,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1698-323-CM25</t>
+          <t>646-137-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7675,17 +7675,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3217.97</v>
+        <v>3272.14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>646-137-CM25</t>
+          <t>3512-5742-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7736,17 +7736,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3272.14</v>
+        <v>861.97</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3512-5742-CM25</t>
+          <t>3512-5748-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>861.97</v>
+        <v>6255.31</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3512-5748-CM25</t>
+          <t>1698-323-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>6255.31</v>
+        <v>3217.97</v>
       </c>
     </row>
     <row r="123">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA PROINMIN SPA</t>
+          <t>Importadora y Comercializadora Proinmin SpA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7960,7 +7960,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3512-5785-CM25</t>
+          <t>539119-10324-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7980,17 +7980,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>825.02</v>
+        <v>3648.24</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1058900-101-CM25</t>
+          <t>3512-5785-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8036,22 +8036,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>959.99</v>
+        <v>825.02</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1574-340-CM25</t>
+          <t>1058900-101-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>980.51</v>
+        <v>959.99</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3512-5858-CM25</t>
+          <t>1574-340-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8153,27 +8153,27 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>10604.02</v>
+        <v>980.51</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3712-1068-CM25</t>
+          <t>3512-5858-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8224,17 +8224,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>4074.06</v>
+        <v>10604.02</v>
       </c>
     </row>
     <row r="129">
@@ -8326,7 +8326,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3512-5880-CM25</t>
+          <t>3712-1068-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8341,22 +8341,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3157.8</v>
+        <v>4074.06</v>
       </c>
     </row>
     <row r="131">
@@ -8448,7 +8448,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4619-42-CM25</t>
+          <t>3512-5880-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8463,22 +8463,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1681.22</v>
+        <v>3157.8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3512-5894-CM25</t>
+          <t>4619-42-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1970.92</v>
+        <v>1681.22</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3512-5903-CM25</t>
+          <t>3512-5894-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1476.35</v>
+        <v>1970.92</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3512-5905-CM25</t>
+          <t>539119-14846-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8646,22 +8646,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>6566.35</v>
+        <v>3075.17</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2555-266-CM25</t>
+          <t>3512-5903-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8707,22 +8707,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2657.52</v>
+        <v>1476.35</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2555-1792-CM25</t>
+          <t>3512-5905-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8768,22 +8768,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8808,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4851.03</v>
+        <v>6566.35</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2711-615-CM25</t>
+          <t>2555-266-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8829,22 +8829,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1387.05</v>
+        <v>2657.52</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3511-810-CM25</t>
+          <t>2555-1792-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8890,22 +8890,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>908.48</v>
+        <v>4851.03</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>707418-236-CM25</t>
+          <t>2711-615-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8976,12 +8976,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1320.44</v>
+        <v>1387.05</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3512-5932-CM25</t>
+          <t>3511-810-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1913.15</v>
+        <v>908.48</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1461054-720-CM25</t>
+          <t>707418-236-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9073,22 +9073,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>4821.49</v>
+        <v>1320.44</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1159-4-CM26</t>
+          <t>3512-5932-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>10472.52</v>
+        <v>1913.15</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3714-2-CM26</t>
+          <t>1461054-720-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>27366.43</v>
+        <v>4821.49</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1159-7-CM26</t>
+          <t>1159-4-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>23125.08</v>
+        <v>10472.52</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3512-44-CM26</t>
+          <t>3714-2-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9317,22 +9317,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1639.1</v>
+        <v>27366.43</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3512-45-CM26</t>
+          <t>1159-7-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>12435.26</v>
+        <v>23125.08</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3511-9-CM26</t>
+          <t>3512-44-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2790.39</v>
+        <v>1639.1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3511-10-CM26</t>
+          <t>3512-45-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2311.27</v>
+        <v>12435.26</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3512-69-CM26</t>
+          <t>3511-9-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>840.64</v>
+        <v>2790.39</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3512-80-CM26</t>
+          <t>3511-10-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>871.65</v>
+        <v>2311.27</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3512-88-CM26</t>
+          <t>3512-69-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>4943.95</v>
+        <v>840.64</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3512-91-CM26</t>
+          <t>3512-80-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>8299</v>
+        <v>871.65</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3511-17-CM26</t>
+          <t>3512-88-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9845,13 +9845,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1124.2</v>
+        <v>4943.95</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3511-18-CM26</t>
+          <t>3512-91-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9906,13 +9906,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1042.59</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3511-24-CM26</t>
+          <t>3511-17-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1754.17</v>
+        <v>1124.2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3512-112-CM26</t>
+          <t>3511-18-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10028,13 +10028,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>8239.74</v>
+        <v>1042.59</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3511-25-CM26</t>
+          <t>3511-24-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1582.32</v>
+        <v>1754.17</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>627786-29-CM26</t>
+          <t>3512-112-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10110,22 +10110,22 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>LORENZINI PAGLIETTINI Y CIA LTDA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>80.565.500-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>12448.9</v>
+        <v>8239.74</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3512-140-CM26</t>
+          <t>3511-25-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>4147.55</v>
+        <v>1582.32</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3512-158-CM26</t>
+          <t>627786-29-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10232,22 +10232,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>LORENZINI PAGLIETTINI Y CIA LTDA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>80.565.500-3</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1304.63</v>
+        <v>12448.9</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3512-159-CM26</t>
+          <t>3512-140-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1997.85</v>
+        <v>4147.55</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1159-30-CM26</t>
+          <t>3512-158-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10394,13 +10394,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>13834.7</v>
+        <v>1304.63</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3714-6-CM26</t>
+          <t>3512-159-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10415,22 +10415,22 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10455,13 +10455,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>12402.4</v>
+        <v>1997.85</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3714-21-CM26</t>
+          <t>1159-30-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10476,22 +10476,22 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>11034.41</v>
+        <v>13834.7</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3511-40-CM26</t>
+          <t>3714-6-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10537,22 +10537,22 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2380.12</v>
+        <v>12402.4</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3512-192-CM26</t>
+          <t>3714-21-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2322.68</v>
+        <v>11034.41</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4295-1-CM26</t>
+          <t>3511-40-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10684,32 +10684,28 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>MOTORSHOP</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.193.188-1</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>103053.47</v>
+        <v>2380.12</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3511-42-CM26</t>
+          <t>3512-192-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10724,7 +10720,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10749,12 +10745,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10764,13 +10760,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>923.61</v>
+        <v>2322.68</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3512-199-CM26</t>
+          <t>4295-1-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10785,7 +10781,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10795,12 +10791,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10810,22 +10806,26 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>MOTORSHOP</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
+          <t>76.193.188-1</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>3963.33</v>
+        <v>103053.47</v>
       </c>
     </row>
     <row r="171">
@@ -10892,7 +10892,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2446-176-CM26</t>
+          <t>3511-42-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10932,12 +10932,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10947,13 +10947,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>8000.05</v>
+        <v>923.61</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2446-177-CM26</t>
+          <t>3512-199-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10968,22 +10968,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10993,12 +10993,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11008,13 +11008,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>7729.08</v>
+        <v>3963.33</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3512-223-CM26</t>
+          <t>2446-176-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>84.634.200-1</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11069,13 +11069,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>870.75</v>
+        <v>8000.05</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3512-227-CM26</t>
+          <t>2446-177-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11090,22 +11090,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11130,13 +11130,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>3791.69</v>
+        <v>7729.08</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1159-36-CM26</t>
+          <t>3512-223-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11176,12 +11176,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>4443.61</v>
+        <v>870.75</v>
       </c>
     </row>
     <row r="177">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11258,7 +11258,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1159-38-CM26</t>
+          <t>1159-36-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11313,13 +11313,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>941.01</v>
+        <v>4443.61</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1002588-42-CM26</t>
+          <t>3512-227-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11329,27 +11329,27 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11374,13 +11374,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1140.49</v>
+        <v>3791.69</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1002588-43-CM26</t>
+          <t>1159-38-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11395,22 +11395,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11435,13 +11435,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>9051.549999999999</v>
+        <v>941.01</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1159-49-CM26</t>
+          <t>1002588-42-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11456,22 +11456,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11496,13 +11496,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>22515.58</v>
+        <v>1140.49</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3682-223-CM26</t>
+          <t>1002588-43-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11542,12 +11542,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>8899.32</v>
+        <v>9051.549999999999</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1430707-1008-CM26</t>
+          <t>1159-49-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11578,22 +11578,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11603,12 +11603,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11618,13 +11618,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>857.64</v>
+        <v>22515.58</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3512-330-CM26</t>
+          <t>3682-223-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11639,22 +11639,22 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11679,13 +11679,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1811.08</v>
+        <v>8899.32</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3511-78-CM26</t>
+          <t>1430707-1008-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11700,22 +11700,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11740,13 +11740,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>4463.69</v>
+        <v>857.64</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3512-347-CM26</t>
+          <t>3512-330-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11786,12 +11786,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11801,13 +11801,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>5814.41</v>
+        <v>1811.08</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3512-365-CM26</t>
+          <t>3511-78-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11847,12 +11847,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11862,13 +11862,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1690.63</v>
+        <v>4463.69</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1173458-2-CM26</t>
+          <t>3512-347-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11878,27 +11878,27 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.980.390-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Ovalle</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11923,13 +11923,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1105.65</v>
+        <v>5814.41</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3712-248-CM26</t>
+          <t>3512-365-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11939,27 +11939,27 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11984,13 +11984,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1559.43</v>
+        <v>1690.63</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2446-366-CM26</t>
+          <t>1173458-2-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12015,12 +12015,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.980.390-6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2317.28</v>
+        <v>1105.65</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2708-194-CM26</t>
+          <t>3712-248-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12071,17 +12071,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12091,12 +12091,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12106,13 +12106,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4657.38</v>
+        <v>1559.43</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3000-454-CM26</t>
+          <t>2446-366-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12127,22 +12127,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12152,12 +12152,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12167,13 +12167,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>5483.33</v>
+        <v>2317.28</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2555-57-CM26</t>
+          <t>2708-194-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12188,22 +12188,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12228,13 +12228,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1793.11</v>
+        <v>4657.38</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1079505-152-CM26</t>
+          <t>3000-454-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12249,22 +12249,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12289,13 +12289,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>18995.56</v>
+        <v>5483.33</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3511-125-CM26</t>
+          <t>2555-57-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12310,22 +12310,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12350,13 +12350,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1076.29</v>
+        <v>1793.11</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>3714-108-CM26</t>
+          <t>1079505-152-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12411,13 +12411,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>5926.09</v>
+        <v>18995.56</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3512-437-CM26</t>
+          <t>3511-125-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12457,12 +12457,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12472,13 +12472,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>5890.92</v>
+        <v>1076.29</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3712-297-CM26</t>
+          <t>3714-108-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3170.23</v>
+        <v>5926.09</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4036-226-CM26</t>
+          <t>3512-437-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12594,13 +12594,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1852.81</v>
+        <v>5890.92</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3512-450-CM26</t>
+          <t>3712-297-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12610,27 +12610,27 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12655,13 +12655,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>4404.9</v>
+        <v>3170.23</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3512-460-CM26</t>
+          <t>4036-226-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12671,12 +12671,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12716,13 +12716,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>6634.71</v>
+        <v>1852.81</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2555-66-CM26</t>
+          <t>3512-450-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12742,17 +12742,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12762,12 +12762,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12777,13 +12777,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1313.56</v>
+        <v>4404.9</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>3712-332-CM26</t>
+          <t>3512-460-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12798,22 +12798,22 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12838,13 +12838,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5711.05</v>
+        <v>6634.71</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3512-447-CM26</t>
+          <t>2555-66-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12859,22 +12859,22 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12884,12 +12884,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12899,13 +12899,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>7966.67</v>
+        <v>1313.56</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>646-50-CM26</t>
+          <t>3712-332-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12960,13 +12960,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>4098.82</v>
+        <v>5711.05</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1057439-3336-CM26</t>
+          <t>3512-447-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12981,22 +12981,22 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13021,13 +13021,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>14440.45</v>
+        <v>7966.67</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1962-268-CM26</t>
+          <t>646-50-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13052,12 +13052,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1124.49</v>
+        <v>4098.82</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1159-106-CM26</t>
+          <t>1057439-3336-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13103,22 +13103,22 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13143,13 +13143,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>16425.14</v>
+        <v>14440.45</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>894358-22-CM26</t>
+          <t>1962-268-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13204,13 +13204,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1448.55</v>
+        <v>1124.49</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>627786-92-CM26</t>
+          <t>1159-106-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13225,22 +13225,22 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13250,12 +13250,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13265,13 +13265,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1146.92</v>
+        <v>16425.14</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>627786-96-CM26</t>
+          <t>894358-22-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13326,13 +13326,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>11909.44</v>
+        <v>1448.55</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1159-113-CM26</t>
+          <t>627786-92-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13347,22 +13347,22 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13387,13 +13387,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1601.29</v>
+        <v>1146.92</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1159-114-CM26</t>
+          <t>627786-96-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13403,27 +13403,27 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13433,12 +13433,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13448,13 +13448,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>15462.16</v>
+        <v>11909.44</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1574-75-CM26</t>
+          <t>1159-113-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13464,27 +13464,27 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13509,13 +13509,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>4609.09</v>
+        <v>1601.29</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1159-138-CM26</t>
+          <t>1159-114-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13570,13 +13570,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>11018.14</v>
+        <v>15462.16</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3712-402-CM26</t>
+          <t>1159-138-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13591,22 +13591,22 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13616,12 +13616,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>MOTORSHOP</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.193.188-1</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13631,13 +13631,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>4913.58</v>
+        <v>11018.14</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3512-547-CM26</t>
+          <t>1574-75-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13652,22 +13652,22 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13677,12 +13677,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13692,13 +13692,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1454.78</v>
+        <v>4609.09</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3512-559-CM26</t>
+          <t>3712-402-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13718,17 +13718,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>MOTORSHOP</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.193.188-1</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13753,13 +13753,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2867.46</v>
+        <v>4913.58</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3512-549-CM26</t>
+          <t>3512-547-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13814,13 +13814,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>6271.4</v>
+        <v>1454.78</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2446-644-CM26</t>
+          <t>3512-559-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13835,22 +13835,22 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13860,12 +13860,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13875,13 +13875,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>39156.32</v>
+        <v>2867.46</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3512-560-CM26</t>
+          <t>3512-549-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13921,12 +13921,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13936,13 +13936,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>4997.56</v>
+        <v>6271.4</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3512-574-CM26</t>
+          <t>539119-1837-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13957,22 +13957,22 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13997,13 +13997,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>8154.58</v>
+        <v>7644.25</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1698-157-CM26</t>
+          <t>539119-1844-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14018,22 +14018,22 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14058,13 +14058,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1917.72</v>
+        <v>7363.21</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>3712-422-CM26</t>
+          <t>2446-644-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14104,12 +14104,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14119,13 +14119,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2747.91</v>
+        <v>39156.32</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1574-84-CM26</t>
+          <t>3512-560-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14140,22 +14140,22 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14165,12 +14165,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14180,13 +14180,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2003.85</v>
+        <v>4997.56</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1574-85-CM26</t>
+          <t>3512-574-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14201,22 +14201,22 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14226,12 +14226,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14241,13 +14241,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>797.33</v>
+        <v>8154.58</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1232565-171-CM26</t>
+          <t>1698-157-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14262,22 +14262,22 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14302,13 +14302,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2492.22</v>
+        <v>1917.72</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1232565-175-CM26</t>
+          <t>3712-422-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14323,22 +14323,22 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14348,12 +14348,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14363,13 +14363,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2613.61</v>
+        <v>2747.91</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3512-590-CM26</t>
+          <t>1574-84-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14384,22 +14384,22 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14409,12 +14409,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14424,13 +14424,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3536.34</v>
+        <v>2003.85</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>3512-562-CM26</t>
+          <t>1574-85-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14445,22 +14445,22 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14485,13 +14485,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>3342.92</v>
+        <v>797.33</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3712-453-CM26</t>
+          <t>1232565-171-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14531,12 +14531,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14546,13 +14546,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1898.89</v>
+        <v>2492.22</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3000-716-CM26</t>
+          <t>1232565-175-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14567,22 +14567,22 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14592,12 +14592,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14607,13 +14607,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>12794.66</v>
+        <v>2613.61</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1159-170-CM26</t>
+          <t>3512-590-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14638,12 +14638,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14653,12 +14653,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14668,13 +14668,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2023.77</v>
+        <v>3536.34</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>3712-451-CM26</t>
+          <t>3512-562-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14684,27 +14684,27 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES TASICA SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>77.268.885-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -14729,13 +14729,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2852.02</v>
+        <v>3342.92</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>707418-92-CM26</t>
+          <t>3712-453-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14745,12 +14745,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -14760,12 +14760,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14775,12 +14775,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -14790,13 +14790,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>835.3</v>
+        <v>1898.89</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3687-181-CM26</t>
+          <t>3000-716-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14806,12 +14806,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14821,12 +14821,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14836,12 +14836,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14851,13 +14851,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>9865.75</v>
+        <v>12794.66</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2446-761-CM26</t>
+          <t>1159-170-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14867,27 +14867,27 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14897,12 +14897,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -14912,13 +14912,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>5417.83</v>
+        <v>2023.77</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2446-762-CM26</t>
+          <t>3712-451-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14943,12 +14943,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>SOCIEDAD DE INVERSIONES TASICA SPA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.268.885-7</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -14973,13 +14973,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>6506.18</v>
+        <v>2852.02</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2446-802-CM26</t>
+          <t>707418-92-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14994,22 +14994,22 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15019,12 +15019,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15034,13 +15034,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>20020.78</v>
+        <v>835.3</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3712-492-CM26</t>
+          <t>2446-762-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15055,22 +15055,22 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15080,12 +15080,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15095,13 +15095,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>11381.64</v>
+        <v>6506.18</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3712-478-CM26</t>
+          <t>3687-181-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15141,12 +15141,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15156,13 +15156,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>12444.99</v>
+        <v>9865.75</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1461054-282-CM26</t>
+          <t>2446-761-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15177,22 +15177,22 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15202,12 +15202,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15217,13 +15217,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>3612.87</v>
+        <v>5417.83</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1430715-156-CM26</t>
+          <t>3712-478-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15238,22 +15238,22 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15263,12 +15263,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15278,13 +15278,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2532.54</v>
+        <v>12444.99</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3512-694-CM26</t>
+          <t>3712-492-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15299,22 +15299,22 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15324,12 +15324,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15339,13 +15339,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2429.45</v>
+        <v>11381.64</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2446-852-CM26</t>
+          <t>2446-802-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15360,12 +15360,12 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -15385,12 +15385,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2202.93</v>
+        <v>20020.78</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2448-779-CM26</t>
+          <t>1461054-282-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15421,7 +15421,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15461,13 +15461,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1180.4</v>
+        <v>3612.87</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1159-213-CM26</t>
+          <t>1430715-156-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15477,12 +15477,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15522,13 +15522,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1494.14</v>
+        <v>2532.54</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1698-224-CM26</t>
+          <t>3512-694-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -15553,12 +15553,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15568,12 +15568,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15583,13 +15583,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>5936.59</v>
+        <v>2429.45</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2446-883-CM26</t>
+          <t>2446-852-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15599,17 +15599,17 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -15629,12 +15629,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>EASY RETAIL S.A. .-</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>76.568.660-1</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15644,13 +15644,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>7665.22</v>
+        <v>2202.93</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2450-818-CM26</t>
+          <t>3712-519-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15660,27 +15660,27 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -15705,13 +15705,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>7035.98</v>
+        <v>9873.530000000001</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3712-542-CM26</t>
+          <t>3509-302-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15721,27 +15721,27 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15751,12 +15751,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -15766,13 +15766,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1971.97</v>
+        <v>4430.78</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2446-760-CM26</t>
+          <t>2448-779-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15782,17 +15782,17 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -15812,12 +15812,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -15827,13 +15827,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>38304.03</v>
+        <v>1180.4</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1159-233-CM26</t>
+          <t>1159-213-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -15888,13 +15888,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>13666.99</v>
+        <v>1494.14</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2446-935-CM26</t>
+          <t>2450-818-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -15919,12 +15919,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15934,12 +15934,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -15949,13 +15949,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>859.83</v>
+        <v>7035.98</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2446-819-CM26</t>
+          <t>1698-224-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -15980,12 +15980,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -15995,12 +15995,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>35641.79</v>
+        <v>5936.59</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2446-863-CM26</t>
+          <t>2446-883-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -16056,12 +16056,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>EASY RETAIL S.A. .-</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
+          <t>76.568.660-1</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16071,13 +16071,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>21356.65</v>
+        <v>7665.22</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1430715-175-CM26</t>
+          <t>3712-542-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -16102,12 +16102,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16117,12 +16117,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16132,13 +16132,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>15395.37</v>
+        <v>1971.97</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3712-558-CM26</t>
+          <t>2446-760-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -16163,12 +16163,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16178,12 +16178,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>84.634.200-1</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16193,13 +16193,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>6429.61</v>
+        <v>38304.03</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3712-564-CM26</t>
+          <t>1159-233-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16254,13 +16254,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4871.19</v>
+        <v>13666.99</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>3512-741-CM26</t>
+          <t>2446-935-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16275,22 +16275,22 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16300,12 +16300,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>84.634.200-1</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16315,13 +16315,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>6538.5</v>
+        <v>859.83</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3712-568-CM26</t>
+          <t>2446-819-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16336,22 +16336,22 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16361,12 +16361,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16376,13 +16376,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>989.41</v>
+        <v>35641.79</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1346282-354-CM26</t>
+          <t>2446-863-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>84.634.200-1</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16437,7 +16437,1593 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
+        <v>21356.65</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1430715-175-CM26</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>61.606.403-7</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="n">
+        <v>15395.37</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>3712-558-CM26</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>6429.61</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>3712-564-CM26</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>4871.19</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>3512-741-CM26</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="n">
+        <v>6538.5</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>3712-568-CM26</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>989.41</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1346282-354-CM26</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="n">
         <v>2335.54</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2446-1031-CM26</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="n">
+        <v>7541.94</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>646-90-CM26</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>61.816.000-9</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="n">
+        <v>8376.34</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>3512-787-CM26</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="n">
+        <v>3042.57</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2446-884-CM26</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M272" s="2" t="n">
+        <v>16820.11</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>3593-335-CM26</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="n">
+        <v>1379.35</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>1159-257-CM26</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="n">
+        <v>3285.92</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>3712-577-CM26</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="n">
+        <v>1334.68</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>527481-86-CM26</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Equilibrium SpA</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="n">
+        <v>9981.559999999999</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>3512-794-CM26</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="n">
+        <v>3188.05</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>3000-929-CM26</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>69.040.800-7</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="n">
+        <v>1099.03</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>3000-927-CM26</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>69.040.800-7</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="n">
+        <v>4316.52</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>3712-603-CM26</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="n">
+        <v>5106.69</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2446-1076-CM26</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="n">
+        <v>2256.86</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>3512-812-CM26</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="n">
+        <v>1642.37</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>3713-123-CM26</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="n">
+        <v>1261.7</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>1079505-595-CM26</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="n">
+        <v>7576.84</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>1242121-488-CM26</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>61.606.404-5</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="n">
+        <v>2699.07</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2446-1125-CM26</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>QUALITY RUBBER S.A.</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>76.097.502-8</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="n">
+        <v>3421.93</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>3512-846-CM26</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="n">
+        <v>1809.95</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>624-223-CM26</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>72.225.700-6</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="n">
+        <v>3438.63</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
@@ -1172,7 +1172,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1298,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1546,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1672,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2042,11 @@
           <t>77.575.038-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2168,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2233,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3396,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3583,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3648,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3713,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3900,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4087,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4518,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4766,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4831,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5872,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5937,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6002,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6189,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6254,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6319,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6567,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6632,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6758,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6823,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6888,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +6953,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7079,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7209,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7274,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7400,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7465,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7530,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7656,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7721,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +7786,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +7912,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +7977,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8164,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8229,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8355,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8420,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8485,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8550,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8676,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +8802,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +8867,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +8932,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +8997,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9184,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9371,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9436,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9684,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9749,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +9936,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10001,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10066,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10131,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10379,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10566,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10631,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10696,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +10822,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11009,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10879,7 +11139,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11001,7 +11265,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11062,7 +11330,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11184,7 +11456,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11367,7 +11643,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11428,7 +11708,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11672,7 +11956,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11794,7 +12082,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11855,7 +12147,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11916,7 +12212,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11977,7 +12277,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12038,7 +12342,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12099,7 +12407,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12282,7 +12594,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12526,7 +12842,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12587,7 +12907,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12770,7 +13094,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12831,7 +13159,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12953,7 +13285,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13014,7 +13350,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13380,7 +13720,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13502,7 +13846,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13746,7 +14094,11 @@
           <t>76.193.188-1</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13807,7 +14159,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13868,7 +14224,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13929,7 +14289,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13990,7 +14354,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14051,7 +14419,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14112,7 +14484,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14173,7 +14549,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14234,7 +14614,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14295,7 +14679,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14356,7 +14744,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14417,7 +14809,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14478,7 +14874,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14661,7 +15061,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14722,7 +15126,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14783,7 +15191,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14844,7 +15256,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15088,7 +15504,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15149,7 +15569,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15332,7 +15756,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15393,7 +15821,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15576,7 +16008,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15637,7 +16073,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15881,7 +16321,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16125,7 +16569,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16186,7 +16634,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16308,7 +16760,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16430,7 +16886,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16552,7 +17012,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16613,7 +17077,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16674,7 +17142,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16735,7 +17207,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16796,7 +17272,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16857,7 +17337,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16979,7 +17463,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17101,7 +17589,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17223,7 +17715,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17345,7 +17841,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +17906,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17467,7 +17971,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17528,7 +18036,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17589,7 +18101,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17650,7 +18166,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17711,7 +18231,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17772,7 +18296,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17833,7 +18361,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17955,7 +18487,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
@@ -1798,7 +1798,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2481,7 +2485,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5262,7 +5270,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5445,7 +5457,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7018,7 +7034,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8294,7 +8314,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M288"/>
+  <dimension ref="A1:M302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2063,7 +2063,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1962-140-CM25</t>
+          <t>3509-147-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2083,17 +2083,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2103,28 +2103,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1260.36</v>
+        <v>10525.94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3509-147-CM25</t>
+          <t>1962-140-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2144,17 +2148,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2164,26 +2168,22 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>10525.94</v>
+        <v>1260.36</v>
       </c>
     </row>
     <row r="29">
@@ -4234,7 +4234,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1232565-150-CM25</t>
+          <t>1159-109-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4254,17 +4254,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4289,13 +4289,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>11121.85</v>
+        <v>6700.15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1159-109-CM25</t>
+          <t>1232565-150-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4350,13 +4350,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6700.15</v>
+        <v>11121.85</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3712-551-CM25</t>
+          <t>1232565-156-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Francisco javier</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4411,13 +4411,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1619.25</v>
+        <v>1460.08</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1232565-156-CM25</t>
+          <t>3712-551-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1460.08</v>
+        <v>1619.25</v>
       </c>
     </row>
     <row r="66">
@@ -4726,7 +4726,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1159-120-CM25</t>
+          <t>3512-5179-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4785,13 +4785,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>16049.12</v>
+        <v>887.96</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3512-5179-CM25</t>
+          <t>1159-120-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>887.96</v>
+        <v>16049.12</v>
       </c>
     </row>
     <row r="72">
@@ -5535,7 +5535,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>539119-4669-CM25</t>
+          <t>539119-4673-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3141.17</v>
+        <v>1057.61</v>
       </c>
     </row>
     <row r="84">
@@ -5657,7 +5657,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>539119-4673-CM25</t>
+          <t>539119-4669-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5712,13 +5712,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1057.61</v>
+        <v>3141.17</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>539119-4678-CM25</t>
+          <t>2708-702-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5758,22 +5758,26 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2916.95</v>
+        <v>2039.87</v>
       </c>
     </row>
     <row r="87">
@@ -5840,7 +5844,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2708-702-CM25</t>
+          <t>539119-4678-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5860,17 +5864,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5880,26 +5884,22 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.038.841-4</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2039.87</v>
+        <v>2916.95</v>
       </c>
     </row>
     <row r="89">
@@ -6157,7 +6157,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3712-852-CM25</t>
+          <t>3512-5484-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6177,17 +6177,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>6446.52</v>
+        <v>10297.09</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3512-5484-CM25</t>
+          <t>3512-5482-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6281,13 +6281,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>10297.09</v>
+        <v>1308.95</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3512-5482-CM25</t>
+          <t>3712-852-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6307,17 +6307,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1308.95</v>
+        <v>6446.52</v>
       </c>
     </row>
     <row r="96">
@@ -6413,7 +6413,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>707418-153-CM25</t>
+          <t>1159-219-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6433,17 +6433,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6468,13 +6468,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3146.58</v>
+        <v>16038.33</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1159-219-CM25</t>
+          <t>3512-5551-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6514,28 +6514,32 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>16038.33</v>
+        <v>3035.48</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3512-5551-CM25</t>
+          <t>707418-153-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6555,17 +6559,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6575,26 +6579,22 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.610.800-0</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3035.48</v>
+        <v>3146.58</v>
       </c>
     </row>
     <row r="100">
@@ -7823,7 +7823,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>646-137-CM25</t>
+          <t>1698-323-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7843,17 +7843,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7878,13 +7878,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3272.14</v>
+        <v>3217.97</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3512-5742-CM25</t>
+          <t>646-137-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7904,17 +7904,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7924,32 +7924,28 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>861.97</v>
+        <v>3272.14</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3512-5748-CM25</t>
+          <t>3512-5742-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8008,13 +8004,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>6255.31</v>
+        <v>861.97</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1698-323-CM25</t>
+          <t>3512-5748-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8039,12 +8035,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8054,22 +8050,26 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3217.97</v>
+        <v>6255.31</v>
       </c>
     </row>
     <row r="123">
@@ -9851,7 +9851,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3511-10-CM26</t>
+          <t>3512-69-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9891,28 +9891,32 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2311.27</v>
+        <v>840.64</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3512-69-CM26</t>
+          <t>3511-10-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9952,26 +9956,22 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>840.64</v>
+        <v>2311.27</v>
       </c>
     </row>
     <row r="153">
@@ -10607,7 +10607,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3512-158-CM26</t>
+          <t>3512-159-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10666,13 +10666,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1304.63</v>
+        <v>1997.85</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3512-159-CM26</t>
+          <t>3512-158-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1997.85</v>
+        <v>1304.63</v>
       </c>
     </row>
     <row r="165">
@@ -11115,7 +11115,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3512-200-CM26</t>
+          <t>3511-42-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11155,32 +11155,28 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>6180.35</v>
+        <v>923.61</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3511-42-CM26</t>
+          <t>3512-200-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11220,22 +11216,26 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>923.61</v>
+        <v>6180.35</v>
       </c>
     </row>
     <row r="173">
@@ -11306,7 +11306,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2446-176-CM26</t>
+          <t>2446-177-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -11346,32 +11346,28 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>8000.05</v>
+        <v>7729.08</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2446-177-CM26</t>
+          <t>2446-176-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11391,7 +11387,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -11411,28 +11407,32 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
+          <t>84.634.200-1</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>7729.08</v>
+        <v>8000.05</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3512-223-CM26</t>
+          <t>3512-227-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11491,13 +11491,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>870.75</v>
+        <v>3791.69</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>627786-33-CM26</t>
+          <t>3512-223-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11517,17 +11517,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11537,22 +11537,26 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>12289.46</v>
+        <v>870.75</v>
       </c>
     </row>
     <row r="178">
@@ -11619,7 +11623,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3512-227-CM26</t>
+          <t>627786-33-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11639,17 +11643,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11659,26 +11663,22 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3791.69</v>
+        <v>12289.46</v>
       </c>
     </row>
     <row r="180">
@@ -11749,7 +11749,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1002588-42-CM26</t>
+          <t>1002588-43-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11804,13 +11804,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1140.49</v>
+        <v>9051.549999999999</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1002588-43-CM26</t>
+          <t>1002588-42-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11865,13 +11865,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>9051.549999999999</v>
+        <v>1140.49</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1159-49-CM26</t>
+          <t>3682-223-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11891,17 +11891,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11911,28 +11911,32 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>22515.58</v>
+        <v>8899.32</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3682-223-CM26</t>
+          <t>1159-49-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11952,17 +11956,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11972,26 +11976,22 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>8899.32</v>
+        <v>22515.58</v>
       </c>
     </row>
     <row r="185">
@@ -12383,7 +12383,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3712-248-CM26</t>
+          <t>2708-194-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12403,17 +12403,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12423,26 +12423,22 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1559.43</v>
+        <v>4657.38</v>
       </c>
     </row>
     <row r="192">
@@ -12509,7 +12505,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2708-194-CM26</t>
+          <t>3712-248-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12529,17 +12525,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12549,22 +12545,26 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
+          <t>77.823.479-3</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>4657.38</v>
+        <v>1559.43</v>
       </c>
     </row>
     <row r="194">
@@ -14070,7 +14070,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3712-402-CM26</t>
+          <t>3512-559-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14090,17 +14090,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14110,12 +14110,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>MOTORSHOP</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>76.193.188-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>4913.58</v>
+        <v>2867.46</v>
       </c>
     </row>
     <row r="219">
@@ -14200,7 +14200,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3512-559-CM26</t>
+          <t>3712-402-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14220,17 +14220,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14240,12 +14240,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>MOTORSHOP</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.193.188-1</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -14259,7 +14259,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2867.46</v>
+        <v>4913.58</v>
       </c>
     </row>
     <row r="221">
@@ -14330,7 +14330,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>539119-1837-CM26</t>
+          <t>539119-1844-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14389,13 +14389,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>7644.25</v>
+        <v>7363.21</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>539119-1844-CM26</t>
+          <t>539119-1837-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14454,13 +14454,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>7363.21</v>
+        <v>7644.25</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2446-644-CM26</t>
+          <t>3512-560-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14480,17 +14480,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -14519,13 +14519,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>39156.32</v>
+        <v>4997.56</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3512-560-CM26</t>
+          <t>3512-574-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14565,12 +14565,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -14584,13 +14584,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4997.56</v>
+        <v>8154.58</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3512-574-CM26</t>
+          <t>2446-644-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14630,12 +14630,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>8154.58</v>
+        <v>39156.32</v>
       </c>
     </row>
     <row r="227">
@@ -14720,7 +14720,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3712-422-CM26</t>
+          <t>1574-84-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14745,12 +14745,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14760,17 +14760,17 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14779,13 +14779,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2747.91</v>
+        <v>2003.85</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1574-84-CM26</t>
+          <t>1232565-171-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14825,32 +14825,28 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2003.85</v>
+        <v>2492.22</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1574-85-CM26</t>
+          <t>3712-422-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14875,12 +14871,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14890,17 +14886,17 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -14909,13 +14905,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>797.33</v>
+        <v>2747.91</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1232565-171-CM26</t>
+          <t>1574-85-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14940,12 +14936,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14955,22 +14951,26 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2492.22</v>
+        <v>797.33</v>
       </c>
     </row>
     <row r="232">
@@ -15037,7 +15037,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3512-590-CM26</t>
+          <t>3512-562-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15096,13 +15096,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>3536.34</v>
+        <v>3342.92</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>3512-562-CM26</t>
+          <t>3512-590-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3342.92</v>
+        <v>3536.34</v>
       </c>
     </row>
     <row r="235">
@@ -15358,7 +15358,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3712-451-CM26</t>
+          <t>707418-92-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15378,17 +15378,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15398,12 +15398,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES TASICA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>77.268.885-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -15413,13 +15413,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2852.02</v>
+        <v>835.3</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>707418-92-CM26</t>
+          <t>3712-451-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15439,17 +15439,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15459,12 +15459,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES TASICA SPA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.268.885-7</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15474,7 +15474,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>835.3</v>
+        <v>2852.02</v>
       </c>
     </row>
     <row r="240">
@@ -15545,7 +15545,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3687-181-CM26</t>
+          <t>2446-761-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15565,17 +15565,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15585,32 +15585,28 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>9865.75</v>
+        <v>5417.83</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2446-761-CM26</t>
+          <t>3687-181-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15630,17 +15626,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15650,22 +15646,26 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr"/>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>5417.83</v>
+        <v>9865.75</v>
       </c>
     </row>
     <row r="243">
@@ -15732,7 +15732,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3712-492-CM26</t>
+          <t>2446-802-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -15791,13 +15791,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>11381.64</v>
+        <v>20020.78</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2446-802-CM26</t>
+          <t>3712-492-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -15856,7 +15856,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>20020.78</v>
+        <v>11381.64</v>
       </c>
     </row>
     <row r="246">
@@ -15923,7 +15923,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1430715-156-CM26</t>
+          <t>2446-852-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15963,22 +15963,26 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>2532.54</v>
+        <v>2202.93</v>
       </c>
     </row>
     <row r="248">
@@ -16049,7 +16053,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2446-852-CM26</t>
+          <t>1430715-156-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16069,17 +16073,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16089,26 +16093,22 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2202.93</v>
+        <v>2532.54</v>
       </c>
     </row>
     <row r="250">
@@ -16610,7 +16610,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2446-760-CM26</t>
+          <t>1159-233-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16635,12 +16635,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16650,32 +16650,28 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>38304.03</v>
+        <v>13666.99</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1159-233-CM26</t>
+          <t>2446-760-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16700,12 +16696,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16715,22 +16711,26 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
+          <t>84.634.200-1</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>13666.99</v>
+        <v>38304.03</v>
       </c>
     </row>
     <row r="260">
@@ -16801,7 +16801,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2446-819-CM26</t>
+          <t>1430715-175-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16821,17 +16821,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16841,12 +16841,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16856,13 +16856,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>35641.79</v>
+        <v>15395.37</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2446-863-CM26</t>
+          <t>2446-819-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -16902,32 +16902,28 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>21356.65</v>
+        <v>35641.79</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1430715-175-CM26</t>
+          <t>2446-863-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16952,12 +16948,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16967,22 +16963,26 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
+          <t>84.634.200-1</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>15395.37</v>
+        <v>21356.65</v>
       </c>
     </row>
     <row r="264">
@@ -17053,7 +17053,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3712-564-CM26</t>
+          <t>3512-741-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17073,17 +17073,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -17112,13 +17112,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>4871.19</v>
+        <v>6538.5</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3512-741-CM26</t>
+          <t>3712-564-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17138,17 +17138,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17158,12 +17158,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -17177,13 +17177,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>6538.5</v>
+        <v>4871.19</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3712-568-CM26</t>
+          <t>1346282-354-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17208,12 +17208,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17223,12 +17223,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -17242,13 +17242,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>989.41</v>
+        <v>2335.54</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1346282-354-CM26</t>
+          <t>3712-568-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17273,12 +17273,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17288,12 +17288,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -17307,7 +17307,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2335.54</v>
+        <v>989.41</v>
       </c>
     </row>
     <row r="269">
@@ -17378,7 +17378,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>646-90-CM26</t>
+          <t>3512-787-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17398,17 +17398,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17418,28 +17418,32 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>8376.34</v>
+        <v>3042.57</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3512-787-CM26</t>
+          <t>646-90-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17459,17 +17463,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17479,26 +17483,22 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3042.57</v>
+        <v>8376.34</v>
       </c>
     </row>
     <row r="272">
@@ -17565,7 +17565,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>3593-335-CM26</t>
+          <t>1159-257-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17585,17 +17585,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17605,32 +17605,28 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1379.35</v>
+        <v>3285.92</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1159-257-CM26</t>
+          <t>3593-335-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17655,12 +17651,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17670,22 +17666,26 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3285.92</v>
+        <v>1379.35</v>
       </c>
     </row>
     <row r="275">
@@ -18012,7 +18012,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3712-603-CM26</t>
+          <t>3512-812-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18037,12 +18037,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18052,12 +18052,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -18071,7 +18071,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5106.69</v>
+        <v>1642.37</v>
       </c>
     </row>
     <row r="281">
@@ -18142,7 +18142,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>3512-812-CM26</t>
+          <t>3712-603-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18162,17 +18162,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18182,12 +18182,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -18201,13 +18201,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1642.37</v>
+        <v>5106.69</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3713-123-CM26</t>
+          <t>2446-1105-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -18232,12 +18232,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18247,12 +18247,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -18266,13 +18266,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1261.7</v>
+        <v>6688.28</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1079505-595-CM26</t>
+          <t>3713-123-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -18297,12 +18297,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18312,12 +18312,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -18331,13 +18331,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>7576.84</v>
+        <v>1261.7</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1242121-488-CM26</t>
+          <t>1079505-595-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18352,7 +18352,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -18362,12 +18362,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18377,12 +18377,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -18396,7 +18396,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2699.07</v>
+        <v>7576.84</v>
       </c>
     </row>
     <row r="286">
@@ -18463,7 +18463,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3512-846-CM26</t>
+          <t>1242121-488-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18478,22 +18478,22 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18522,68 +18522,962 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1809.95</v>
+        <v>2699.07</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
+          <t>3512-846-CM26</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="n">
+        <v>1809.95</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
           <t>624-223-CM26</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2239-9-LR23</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="D289" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
+      <c r="E289" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
+      <c r="F289" t="inlineStr">
         <is>
           <t>72.225.700-6</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
+      <c r="G289" t="inlineStr">
         <is>
           <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
         <is>
           <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
-      <c r="J288" t="inlineStr">
+      <c r="J289" t="inlineStr">
         <is>
           <t>77.676.860-k</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M288" s="2" t="n">
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="n">
         <v>3438.63</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>3512-872-CM26</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="n">
+        <v>12357.63</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>539119-3167-CM26</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>60.505.720-9</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="n">
+        <v>5906.97</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>539119-3166-CM26</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>60.505.720-9</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="n">
+        <v>6642.43</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>539119-3165-CM26</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>60.505.720-9</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>COMERCIAL TREBOL LIMITADA</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>77.601.801-5</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="n">
+        <v>7257.06</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>539119-3164-CM26</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>60.505.720-9</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>COMERCIAL TREBOL LIMITADA</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>77.601.801-5</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="n">
+        <v>859.84</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>539119-3163-CM26</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>60.505.720-9</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="n">
+        <v>1995.84</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>3593-366-CM26</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="n">
+        <v>3310.08</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>3712-703-CM26</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="n">
+        <v>5654.55</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>3512-908-CM26</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="n">
+        <v>3519.57</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>1159-276-CM26</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="n">
+        <v>15962.43</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>3712-700-CM26</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>76.397.758-7</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="n">
+        <v>2881.01</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2555-190-CM26</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Treck S.A.</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>96.542.490-3</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="n">
+        <v>1459.69</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2555-191-CM26</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Treck S.A.</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>96.542.490-3</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="n">
+        <v>2652.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
@@ -9497,7 +9497,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M302"/>
+  <dimension ref="A1:M305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2063,7 +2063,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3509-147-CM25</t>
+          <t>1962-140-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2083,17 +2083,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2103,32 +2103,28 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>10525.94</v>
+        <v>1260.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1962-140-CM25</t>
+          <t>3509-147-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2148,17 +2144,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2168,22 +2164,26 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1260.36</v>
+        <v>10525.94</v>
       </c>
     </row>
     <row r="29">
@@ -8136,7 +8136,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>539119-10324-CM25</t>
+          <t>3512-5785-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8156,17 +8156,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8195,13 +8195,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3648.24</v>
+        <v>825.02</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3512-5785-CM25</t>
+          <t>539119-10324-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8221,17 +8221,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8241,12 +8241,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>825.02</v>
+        <v>3648.24</v>
       </c>
     </row>
     <row r="126">
@@ -8396,7 +8396,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3512-5858-CM25</t>
+          <t>3712-1080-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8455,13 +8455,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>10604.02</v>
+        <v>2125.86</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3712-1080-CM25</t>
+          <t>3512-5858-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8481,17 +8481,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2125.86</v>
+        <v>10604.02</v>
       </c>
     </row>
     <row r="130">
@@ -8908,7 +8908,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3512-5903-CM25</t>
+          <t>3512-5905-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8967,13 +8967,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1476.35</v>
+        <v>6566.35</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3512-5905-CM25</t>
+          <t>3512-5903-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>6566.35</v>
+        <v>1476.35</v>
       </c>
     </row>
     <row r="138">
@@ -9851,7 +9851,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3512-69-CM26</t>
+          <t>3511-10-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9891,32 +9891,28 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>840.64</v>
+        <v>2311.27</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3511-10-CM26</t>
+          <t>3512-69-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9956,28 +9952,32 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2311.27</v>
+        <v>840.64</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3512-80-CM26</t>
+          <t>3512-91-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10036,13 +10036,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>871.65</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3512-88-CM26</t>
+          <t>3512-80-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10101,13 +10101,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4943.95</v>
+        <v>871.65</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3512-91-CM26</t>
+          <t>3512-88-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10166,13 +10166,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>8299</v>
+        <v>4943.95</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3511-17-CM26</t>
+          <t>3511-18-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10227,13 +10227,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1124.2</v>
+        <v>1042.59</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3511-18-CM26</t>
+          <t>3511-17-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1042.59</v>
+        <v>1124.2</v>
       </c>
     </row>
     <row r="158">
@@ -10798,7 +10798,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3714-6-CM26</t>
+          <t>3714-21-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10838,32 +10838,28 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>12402.4</v>
+        <v>11034.41</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3714-21-CM26</t>
+          <t>3714-6-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10903,22 +10899,26 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>11034.41</v>
+        <v>12402.4</v>
       </c>
     </row>
     <row r="168">
@@ -11115,7 +11115,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3511-42-CM26</t>
+          <t>3512-200-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11155,28 +11155,32 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>923.61</v>
+        <v>6180.35</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3512-200-CM26</t>
+          <t>3512-199-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11235,13 +11239,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>6180.35</v>
+        <v>3963.33</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3512-199-CM26</t>
+          <t>3511-42-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11281,26 +11285,22 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>3963.33</v>
+        <v>923.61</v>
       </c>
     </row>
     <row r="174">
@@ -11432,7 +11432,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3512-227-CM26</t>
+          <t>3512-223-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11491,13 +11491,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3791.69</v>
+        <v>870.75</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3512-223-CM26</t>
+          <t>1159-36-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11517,17 +11517,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11537,32 +11537,28 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.583.479-1</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>870.75</v>
+        <v>4443.61</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1159-36-CM26</t>
+          <t>627786-33-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11587,12 +11583,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11602,12 +11598,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11617,13 +11613,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>4443.61</v>
+        <v>12289.46</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>627786-33-CM26</t>
+          <t>3512-227-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11643,17 +11639,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11663,22 +11659,26 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>12289.46</v>
+        <v>3791.69</v>
       </c>
     </row>
     <row r="180">
@@ -11871,7 +11871,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3682-223-CM26</t>
+          <t>1159-49-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11911,32 +11911,28 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>8899.32</v>
+        <v>22515.58</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1159-49-CM26</t>
+          <t>3682-223-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11961,12 +11957,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11976,22 +11972,26 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>22515.58</v>
+        <v>8899.32</v>
       </c>
     </row>
     <row r="185">
@@ -13261,7 +13261,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3712-332-CM26</t>
+          <t>3512-447-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13281,17 +13281,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -13320,13 +13320,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>5711.05</v>
+        <v>7966.67</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3512-447-CM26</t>
+          <t>3712-332-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13346,17 +13346,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>7966.67</v>
+        <v>5711.05</v>
       </c>
     </row>
     <row r="207">
@@ -14135,7 +14135,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3512-547-CM26</t>
+          <t>3712-402-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14155,17 +14155,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14175,12 +14175,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>MOTORSHOP</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.193.188-1</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -14194,13 +14194,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1454.78</v>
+        <v>4913.58</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3712-402-CM26</t>
+          <t>3512-547-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14220,17 +14220,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14240,12 +14240,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>MOTORSHOP</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.193.188-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -14259,7 +14259,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>4913.58</v>
+        <v>1454.78</v>
       </c>
     </row>
     <row r="221">
@@ -14330,7 +14330,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>539119-1844-CM26</t>
+          <t>539119-1837-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14389,13 +14389,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>7363.21</v>
+        <v>7644.25</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>539119-1837-CM26</t>
+          <t>539119-1844-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14454,13 +14454,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>7644.25</v>
+        <v>7363.21</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>3512-560-CM26</t>
+          <t>2446-644-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14480,17 +14480,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -14519,13 +14519,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>4997.56</v>
+        <v>39156.32</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3512-574-CM26</t>
+          <t>3512-560-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14565,12 +14565,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -14584,13 +14584,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>8154.58</v>
+        <v>4997.56</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2446-644-CM26</t>
+          <t>3512-574-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14630,12 +14630,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>39156.32</v>
+        <v>8154.58</v>
       </c>
     </row>
     <row r="227">
@@ -14785,7 +14785,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1232565-171-CM26</t>
+          <t>1574-85-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14825,28 +14825,32 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2492.22</v>
+        <v>797.33</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>3712-422-CM26</t>
+          <t>1232565-171-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14871,12 +14875,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14886,32 +14890,28 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2747.91</v>
+        <v>2492.22</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1574-85-CM26</t>
+          <t>3712-422-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14936,12 +14936,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14951,17 +14951,17 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -14970,7 +14970,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>797.33</v>
+        <v>2747.91</v>
       </c>
     </row>
     <row r="232">
@@ -15167,7 +15167,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3712-453-CM26</t>
+          <t>3000-716-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15187,17 +15187,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15207,17 +15207,17 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -15226,13 +15226,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1898.89</v>
+        <v>12794.66</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3000-716-CM26</t>
+          <t>1159-170-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15252,17 +15252,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15272,32 +15272,28 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>12794.66</v>
+        <v>2023.77</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1159-170-CM26</t>
+          <t>3712-453-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15322,12 +15318,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15337,22 +15333,26 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr"/>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2023.77</v>
+        <v>1898.89</v>
       </c>
     </row>
     <row r="238">
@@ -15671,7 +15671,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3712-478-CM26</t>
+          <t>2446-802-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15711,28 +15711,32 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr"/>
+          <t>76.532.399-1</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>12444.99</v>
+        <v>20020.78</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2446-802-CM26</t>
+          <t>3712-492-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15757,12 +15761,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15772,12 +15776,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -15791,13 +15795,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>20020.78</v>
+        <v>11381.64</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3712-492-CM26</t>
+          <t>3712-478-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15837,26 +15841,22 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>11381.64</v>
+        <v>12444.99</v>
       </c>
     </row>
     <row r="246">
@@ -16175,7 +16175,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3509-302-CM26</t>
+          <t>2448-779-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16200,12 +16200,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16215,12 +16215,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -16230,13 +16230,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>4430.78</v>
+        <v>1180.4</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2448-779-CM26</t>
+          <t>3509-302-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16261,12 +16261,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16276,12 +16276,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1180.4</v>
+        <v>4430.78</v>
       </c>
     </row>
     <row r="253">
@@ -16362,7 +16362,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2450-818-CM26</t>
+          <t>2446-883-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16402,12 +16402,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>EASY RETAIL S.A. .-</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.568.660-1</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -16417,13 +16417,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>7035.98</v>
+        <v>7665.22</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1698-224-CM26</t>
+          <t>2450-818-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16443,17 +16443,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16463,12 +16463,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -16478,13 +16478,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>5936.59</v>
+        <v>7035.98</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2446-883-CM26</t>
+          <t>1698-224-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16504,17 +16504,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>EASY RETAIL S.A. .-</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.568.660-1</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16539,7 +16539,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>7665.22</v>
+        <v>5936.59</v>
       </c>
     </row>
     <row r="257">
@@ -16862,7 +16862,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2446-819-CM26</t>
+          <t>2446-863-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16902,28 +16902,32 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
+          <t>84.634.200-1</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>35641.79</v>
+        <v>21356.65</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2446-863-CM26</t>
+          <t>2446-819-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16963,26 +16967,22 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>21356.65</v>
+        <v>35641.79</v>
       </c>
     </row>
     <row r="264">
@@ -17504,7 +17504,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2446-884-CM26</t>
+          <t>3593-335-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17544,22 +17544,26 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>16820.11</v>
+        <v>1379.35</v>
       </c>
     </row>
     <row r="273">
@@ -17626,7 +17630,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>3593-335-CM26</t>
+          <t>2446-884-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17651,12 +17655,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17666,26 +17670,22 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1379.35</v>
+        <v>16820.11</v>
       </c>
     </row>
     <row r="275">
@@ -17882,7 +17882,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3000-929-CM26</t>
+          <t>3712-603-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17902,17 +17902,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17941,13 +17941,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1099.03</v>
+        <v>5106.69</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3000-927-CM26</t>
+          <t>2446-1076-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17972,12 +17972,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17987,12 +17987,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -18006,13 +18006,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>4316.52</v>
+        <v>2256.86</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3512-812-CM26</t>
+          <t>3000-927-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18037,12 +18037,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18052,12 +18052,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -18071,13 +18071,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1642.37</v>
+        <v>4316.52</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2446-1076-CM26</t>
+          <t>3000-929-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18102,12 +18102,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18117,12 +18117,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -18136,13 +18136,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2256.86</v>
+        <v>1099.03</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>3712-603-CM26</t>
+          <t>3512-812-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18162,17 +18162,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18182,12 +18182,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -18201,7 +18201,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>5106.69</v>
+        <v>1642.37</v>
       </c>
     </row>
     <row r="283">
@@ -18402,7 +18402,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2446-1125-CM26</t>
+          <t>1242121-488-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18422,17 +18422,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18442,28 +18442,32 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>QUALITY RUBBER S.A.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>3421.93</v>
+        <v>2699.07</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1242121-488-CM26</t>
+          <t>2446-1125-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18483,17 +18487,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18503,26 +18507,22 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.097.502-8</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>2699.07</v>
+        <v>3421.93</v>
       </c>
     </row>
     <row r="288">
@@ -18719,7 +18719,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>539119-3167-CM26</t>
+          <t>539119-3163-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18778,13 +18778,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>5906.97</v>
+        <v>1995.84</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>539119-3166-CM26</t>
+          <t>539119-3164-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18824,17 +18824,17 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIAL TREBOL LIMITADA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.601.801-5</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -18843,7 +18843,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>6642.43</v>
+        <v>859.84</v>
       </c>
     </row>
     <row r="293">
@@ -18914,7 +18914,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>539119-3164-CM26</t>
+          <t>539119-3166-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18954,17 +18954,17 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>COMERCIAL TREBOL LIMITADA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.601.801-5</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -18973,13 +18973,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>859.84</v>
+        <v>6642.43</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>539119-3163-CM26</t>
+          <t>539119-3167-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19038,7 +19038,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1995.84</v>
+        <v>5906.97</v>
       </c>
     </row>
     <row r="296">
@@ -19174,7 +19174,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3512-908-CM26</t>
+          <t>3712-700-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19199,12 +19199,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19214,26 +19214,22 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.397.758-7</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3519.57</v>
+        <v>2881.01</v>
       </c>
     </row>
     <row r="299">
@@ -19300,7 +19296,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3712-700-CM26</t>
+          <t>3512-908-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19325,12 +19321,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19340,28 +19336,32 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2881.01</v>
+        <v>3519.57</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2555-190-CM26</t>
+          <t>3712-699-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19386,12 +19386,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19401,12 +19401,12 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>76.097.502-8</t>
         </is>
       </c>
       <c r="K301" t="inlineStr"/>
@@ -19416,68 +19416,255 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1459.69</v>
+        <v>1201.89</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
+          <t>3512-917-CM26</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="n">
+        <v>4034.59</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2555-190-CM26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Treck S.A.</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>96.542.490-3</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>1459.69</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
           <t>2555-191-CM26</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2239-9-LR23</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
+      <c r="D304" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
+      <c r="E304" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
+      <c r="F304" t="inlineStr">
         <is>
           <t>61.313.000-4</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr">
+      <c r="G304" t="inlineStr">
         <is>
           <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
         <is>
           <t>Treck S.A.</t>
         </is>
       </c>
-      <c r="J302" t="inlineStr">
+      <c r="J304" t="inlineStr">
         <is>
           <t>96.542.490-3</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M302" s="2" t="n">
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="n">
         <v>2652.71</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1962-702-CM26</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>61.004.012-8</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>844.14</v>
       </c>
     </row>
   </sheetData>
